--- a/employment_xlsx/PECH_PROFORMA_INVOICE.xlsx
+++ b/employment_xlsx/PECH_PROFORMA_INVOICE.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,6 +66,34 @@
       <b val="1"/>
       <color rgb="001B2838"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000099CC"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00F5A623"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00888888"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00E8F4F8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00AAAAAA"/>
+      <sz val="7"/>
     </font>
   </fonts>
   <fills count="9">
@@ -158,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -194,6 +222,21 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -269,6 +312,66 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="628650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="628650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -558,8 +661,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -576,57 +680,31 @@
     <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="6" customHeight="1">
-      <c r="A1" s="1" t="inlineStr"/>
-      <c r="B1" s="1" t="inlineStr"/>
-      <c r="C1" s="1" t="inlineStr"/>
-      <c r="D1" s="1" t="inlineStr"/>
-      <c r="E1" s="1" t="inlineStr"/>
-      <c r="F1" s="1" t="inlineStr"/>
-      <c r="G1" s="1" t="inlineStr"/>
-      <c r="H1" s="1" t="inlineStr"/>
-      <c r="I1" s="1" t="inlineStr"/>
-      <c r="J1" s="1" t="inlineStr"/>
-      <c r="K1" s="1" t="inlineStr"/>
-      <c r="L1" s="1" t="inlineStr"/>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>PECH GROUP HOLDINGS LTD</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>PROFORMA INVOICE</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="4" customHeight="1">
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Technology &amp; Infrastructure Enablers for People</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="2" customHeight="1">
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
@@ -635,223 +713,151 @@
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Confidential</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="8" customHeight="1"/>
+    <row r="7" ht="8" customHeight="1">
+      <c r="A7" s="1" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr"/>
+      <c r="G7" s="1" t="inlineStr"/>
+      <c r="H7" s="1" t="inlineStr"/>
+      <c r="I7" s="1" t="inlineStr"/>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr"/>
+      <c r="L7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>PROFORMA INVOICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Pre-Sales Quotation Register  |  CONFIDENTIAL</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-    </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="1" t="n"/>
-      <c r="H6" s="1" t="n"/>
-      <c r="I6" s="1" t="n"/>
-      <c r="J6" s="1" t="n"/>
-      <c r="K6" s="1" t="n"/>
-      <c r="L6" s="1" t="n"/>
-    </row>
-    <row r="7" ht="8" customHeight="1"/>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="1" t="n"/>
+      <c r="H12" s="1" t="n"/>
+      <c r="I12" s="1" t="n"/>
+      <c r="J12" s="1" t="n"/>
+      <c r="K12" s="1" t="n"/>
+      <c r="L12" s="1" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  PROFORMA INVOICE REGISTER</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
-      <c r="K8" s="8" t="n"/>
-      <c r="L8" s="8" t="n"/>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Proforma No.</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Client Name</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>Subtotal (NGN)</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>VAT 7.5%</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>Valid Until</t>
         </is>
       </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>Converted to Invoice</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr">
         <is>
           <t>Invoice No.</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="10" t="n"/>
-      <c r="I10" s="10" t="n"/>
-      <c r="J10" s="10" t="n"/>
-      <c r="K10" s="10" t="n"/>
-      <c r="L10" s="10" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="11" t="n"/>
-      <c r="J11" s="11" t="n"/>
-      <c r="K11" s="11" t="n"/>
-      <c r="L11" s="11" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="n"/>
-      <c r="K12" s="10" t="n"/>
-      <c r="L12" s="10" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="11" t="n"/>
-      <c r="K13" s="11" t="n"/>
-      <c r="L13" s="11" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="10" t="n"/>
-      <c r="I14" s="10" t="n"/>
-      <c r="J14" s="10" t="n"/>
-      <c r="K14" s="10" t="n"/>
-      <c r="L14" s="10" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="11" t="n"/>
-      <c r="L15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B16" s="10" t="n"/>
       <c r="C16" s="10" t="n"/>
@@ -867,7 +873,7 @@
     </row>
     <row r="17">
       <c r="A17" s="11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B17" s="11" t="n"/>
       <c r="C17" s="11" t="n"/>
@@ -883,7 +889,7 @@
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="10" t="n"/>
@@ -899,7 +905,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B19" s="11" t="n"/>
       <c r="C19" s="11" t="n"/>
@@ -915,7 +921,7 @@
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="10" t="n"/>
@@ -931,7 +937,7 @@
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B21" s="11" t="n"/>
       <c r="C21" s="11" t="n"/>
@@ -947,7 +953,7 @@
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B22" s="10" t="n"/>
       <c r="C22" s="10" t="n"/>
@@ -963,7 +969,7 @@
     </row>
     <row r="23">
       <c r="A23" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B23" s="11" t="n"/>
       <c r="C23" s="11" t="n"/>
@@ -979,7 +985,7 @@
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="10" t="n"/>
@@ -995,7 +1001,7 @@
     </row>
     <row r="25">
       <c r="A25" s="11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B25" s="11" t="n"/>
       <c r="C25" s="11" t="n"/>
@@ -1011,7 +1017,7 @@
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="10" t="n"/>
@@ -1027,7 +1033,7 @@
     </row>
     <row r="27">
       <c r="A27" s="11" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B27" s="11" t="n"/>
       <c r="C27" s="11" t="n"/>
@@ -1043,7 +1049,7 @@
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="10" t="n"/>
@@ -1059,7 +1065,7 @@
     </row>
     <row r="29">
       <c r="A29" s="11" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B29" s="11" t="n"/>
       <c r="C29" s="11" t="n"/>
@@ -1075,7 +1081,7 @@
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="10" t="n"/>
@@ -1091,7 +1097,7 @@
     </row>
     <row r="31">
       <c r="A31" s="11" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B31" s="11" t="n"/>
       <c r="C31" s="11" t="n"/>
@@ -1107,7 +1113,7 @@
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B32" s="10" t="n"/>
       <c r="C32" s="10" t="n"/>
@@ -1123,7 +1129,7 @@
     </row>
     <row r="33">
       <c r="A33" s="11" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B33" s="11" t="n"/>
       <c r="C33" s="11" t="n"/>
@@ -1139,7 +1145,7 @@
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="10" t="n"/>
@@ -1155,7 +1161,7 @@
     </row>
     <row r="35">
       <c r="A35" s="11" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
@@ -1171,7 +1177,7 @@
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B36" s="10" t="n"/>
       <c r="C36" s="10" t="n"/>
@@ -1187,7 +1193,7 @@
     </row>
     <row r="37">
       <c r="A37" s="11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B37" s="11" t="n"/>
       <c r="C37" s="11" t="n"/>
@@ -1203,7 +1209,7 @@
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B38" s="10" t="n"/>
       <c r="C38" s="10" t="n"/>
@@ -1219,7 +1225,7 @@
     </row>
     <row r="39">
       <c r="A39" s="11" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
@@ -1233,58 +1239,187 @@
       <c r="K39" s="11" t="n"/>
       <c r="L39" s="11" t="n"/>
     </row>
+    <row r="40">
+      <c r="A40" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="10" t="n"/>
+      <c r="J40" s="10" t="n"/>
+      <c r="K40" s="10" t="n"/>
+      <c r="L40" s="10" t="n"/>
+    </row>
     <row r="41" ht="3" customHeight="1">
-      <c r="A41" s="5" t="n"/>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="n"/>
-      <c r="L41" s="5" t="n"/>
+      <c r="A41" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="11" t="n"/>
+      <c r="G41" s="11" t="n"/>
+      <c r="H41" s="11" t="n"/>
+      <c r="I41" s="11" t="n"/>
+      <c r="J41" s="11" t="n"/>
+      <c r="K41" s="11" t="n"/>
+      <c r="L41" s="11" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="A42" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="10" t="n"/>
+      <c r="J42" s="10" t="n"/>
+      <c r="K42" s="10" t="n"/>
+      <c r="L42" s="10" t="n"/>
+    </row>
+    <row r="43" ht="3" customHeight="1">
+      <c r="A43" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
+      <c r="G43" s="11" t="n"/>
+      <c r="H43" s="11" t="n"/>
+      <c r="I43" s="11" t="n"/>
+      <c r="J43" s="11" t="n"/>
+      <c r="K43" s="11" t="n"/>
+      <c r="L43" s="11" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="10" t="n"/>
+      <c r="J44" s="10" t="n"/>
+      <c r="K44" s="10" t="n"/>
+      <c r="L44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="11" t="n"/>
+      <c r="G45" s="11" t="n"/>
+      <c r="H45" s="11" t="n"/>
+      <c r="I45" s="11" t="n"/>
+      <c r="J45" s="11" t="n"/>
+      <c r="K45" s="11" t="n"/>
+      <c r="L45" s="11" t="n"/>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="5" t="n"/>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
         </is>
       </c>
-      <c r="B42" s="13" t="n"/>
-      <c r="C42" s="13" t="n"/>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="13" t="n"/>
-      <c r="H42" s="13" t="n"/>
-      <c r="I42" s="13" t="n"/>
-      <c r="J42" s="13" t="n"/>
-      <c r="K42" s="13" t="n"/>
-      <c r="L42" s="13" t="n"/>
-    </row>
-    <row r="43" ht="3" customHeight="1">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="1" t="n"/>
-      <c r="C43" s="1" t="n"/>
-      <c r="D43" s="1" t="n"/>
-      <c r="E43" s="1" t="n"/>
-      <c r="F43" s="1" t="n"/>
-      <c r="G43" s="1" t="n"/>
-      <c r="H43" s="1" t="n"/>
-      <c r="I43" s="1" t="n"/>
-      <c r="J43" s="1" t="n"/>
-      <c r="K43" s="1" t="n"/>
-      <c r="L43" s="1" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n"/>
+      <c r="B49" s="1" t="n"/>
+      <c r="C49" s="1" t="n"/>
+      <c r="D49" s="1" t="n"/>
+      <c r="E49" s="1" t="n"/>
+      <c r="F49" s="1" t="n"/>
+      <c r="G49" s="1" t="n"/>
+      <c r="H49" s="1" t="n"/>
+      <c r="I49" s="1" t="n"/>
+      <c r="J49" s="1" t="n"/>
+      <c r="K49" s="1" t="n"/>
+      <c r="L49" s="1" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>Confidential — PECH Group Holdings Ltd — Lagos, Nigeria — pechgroupholdings.tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n"/>
+      <c r="B55" s="1" t="n"/>
+      <c r="C55" s="1" t="n"/>
+      <c r="D55" s="1" t="n"/>
+      <c r="E55" s="1" t="n"/>
+      <c r="F55" s="1" t="n"/>
+      <c r="G55" s="1" t="n"/>
+      <c r="H55" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A53:H53"/>
     <mergeCell ref="A42:L42"/>
+    <mergeCell ref="A54:H54"/>
     <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A52:H52"/>
     <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A3:L3"/>
   </mergeCells>
   <dataValidations count="2">
@@ -1297,6 +1432,15 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;8 PECH Group Holdings Ltd | Confidential</oddHeader>
+    <oddFooter>&amp;C&amp;7 PECH Group Holdings Ltd | Lagos, Nigeria | pechgroupholdings.tech</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1304,8 +1448,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1316,127 +1461,105 @@
     <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="6" customHeight="1">
-      <c r="A1" s="1" t="inlineStr"/>
-      <c r="B1" s="1" t="inlineStr"/>
-      <c r="C1" s="1" t="inlineStr"/>
-      <c r="D1" s="1" t="inlineStr"/>
-      <c r="E1" s="1" t="inlineStr"/>
-      <c r="F1" s="1" t="inlineStr"/>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>PECH GROUP HOLDINGS LTD</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>PROFORMA INVOICE</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="4" customHeight="1">
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Technology &amp; Infrastructure Enablers for People</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="2" customHeight="1">
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Confidential</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="8" customHeight="1"/>
+    <row r="7" ht="8" customHeight="1">
+      <c r="A7" s="1" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>PROFORMA INVOICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Pre-Sale Estimate  |  CONFIDENTIAL</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-    </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="1" t="n"/>
-      <c r="E6" s="1" t="n"/>
-      <c r="F6" s="1" t="n"/>
-    </row>
-    <row r="7" ht="8" customHeight="1"/>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PROFORMA DETAILS</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Proforma No.:</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Date:</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>Valid Until:</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>Project Ref.:</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="n"/>
-    </row>
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="1" t="n"/>
+      <c r="E12" s="1" t="n"/>
+      <c r="F12" s="1" t="n"/>
+    </row>
+    <row r="13"/>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CLIENT INFORMATION</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
+          <t xml:space="preserve">  PROFORMA DETAILS</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Client Name:</t>
+          <t>Proforma No.:</t>
         </is>
       </c>
       <c r="C15" s="15" t="n"/>
@@ -1444,7 +1567,7 @@
     <row r="16" ht="24" customHeight="1">
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>Company:</t>
+          <t>Date:</t>
         </is>
       </c>
       <c r="C16" s="15" t="n"/>
@@ -1452,7 +1575,7 @@
     <row r="17" ht="24" customHeight="1">
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>Address:</t>
+          <t>Valid Until:</t>
         </is>
       </c>
       <c r="C17" s="15" t="n"/>
@@ -1460,35 +1583,31 @@
     <row r="18" ht="24" customHeight="1">
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>Phone:</t>
+          <t>Project Ref.:</t>
         </is>
       </c>
       <c r="C18" s="15" t="n"/>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>Email:</t>
-        </is>
-      </c>
-      <c r="C19" s="15" t="n"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CLIENT INFORMATION</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ITEMS / SERVICES</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Client Name:</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Item 1 — Description / Qty / Price:</t>
+          <t>Company:</t>
         </is>
       </c>
       <c r="C22" s="15" t="n"/>
@@ -1496,7 +1615,7 @@
     <row r="23" ht="24" customHeight="1">
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>Item 2 — Description / Qty / Price:</t>
+          <t>Address:</t>
         </is>
       </c>
       <c r="C23" s="15" t="n"/>
@@ -1504,7 +1623,7 @@
     <row r="24" ht="24" customHeight="1">
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>Item 3 — Description / Qty / Price:</t>
+          <t>Phone:</t>
         </is>
       </c>
       <c r="C24" s="15" t="n"/>
@@ -1512,31 +1631,23 @@
     <row r="25" ht="24" customHeight="1">
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Item 4 — Description / Qty / Price:</t>
+          <t>Email:</t>
         </is>
       </c>
       <c r="C25" s="15" t="n"/>
     </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>Item 5 — Description / Qty / Price:</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="n"/>
-    </row>
+    <row r="26" ht="24" customHeight="1"/>
     <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>Item 6 — Description / Qty / Price:</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="n"/>
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ITEMS / SERVICES</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>Item 7 — Description / Qty / Price:</t>
+          <t>Item 1 — Description / Qty / Price:</t>
         </is>
       </c>
       <c r="C28" s="15" t="n"/>
@@ -1544,27 +1655,31 @@
     <row r="29" ht="24" customHeight="1">
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Item 8 — Description / Qty / Price:</t>
+          <t>Item 2 — Description / Qty / Price:</t>
         </is>
       </c>
       <c r="C29" s="15" t="n"/>
     </row>
+    <row r="30">
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Item 3 — Description / Qty / Price:</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="n"/>
+    </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  SUMMARY</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="8" t="n"/>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Item 4 — Description / Qty / Price:</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="n"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>Subtotal:</t>
+          <t>Item 5 — Description / Qty / Price:</t>
         </is>
       </c>
       <c r="C32" s="15" t="n"/>
@@ -1572,7 +1687,7 @@
     <row r="33" ht="24" customHeight="1">
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>VAT @ 7.5%:</t>
+          <t>Item 6 — Description / Qty / Price:</t>
         </is>
       </c>
       <c r="C33" s="15" t="n"/>
@@ -1580,7 +1695,7 @@
     <row r="34" ht="24" customHeight="1">
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>Discount:</t>
+          <t>Item 7 — Description / Qty / Price:</t>
         </is>
       </c>
       <c r="C34" s="15" t="n"/>
@@ -1588,35 +1703,31 @@
     <row r="35" ht="24" customHeight="1">
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>GRAND TOTAL:</t>
+          <t>Item 8 — Description / Qty / Price:</t>
         </is>
       </c>
       <c r="C35" s="15" t="n"/>
     </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>Amount in Words:</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="n"/>
+    <row r="36" ht="24" customHeight="1"/>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  AUTHORIZATION</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="n"/>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Subtotal:</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Prepared By:</t>
+          <t>VAT @ 7.5%:</t>
         </is>
       </c>
       <c r="C39" s="15" t="n"/>
@@ -1624,7 +1735,7 @@
     <row r="40" ht="24" customHeight="1">
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>Signature:</t>
+          <t>Discount:</t>
         </is>
       </c>
       <c r="C40" s="15" t="n"/>
@@ -1632,52 +1743,143 @@
     <row r="41" ht="24" customHeight="1">
       <c r="B41" s="14" t="inlineStr">
         <is>
+          <t>GRAND TOTAL:</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="n"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>Amount in Words:</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="n"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="3" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AUTHORIZATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>Prepared By:</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="n"/>
+    </row>
+    <row r="46" ht="3" customHeight="1">
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Signature:</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="n"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="14" t="inlineStr">
+        <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="C41" s="15" t="n"/>
-    </row>
-    <row r="44" ht="3" customHeight="1">
-      <c r="A44" s="5" t="n"/>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="C47" s="15" t="n"/>
+    </row>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50">
+      <c r="A50" s="5" t="n"/>
+      <c r="B50" s="5" t="n"/>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
         </is>
       </c>
-      <c r="B45" s="13" t="n"/>
-      <c r="C45" s="13" t="n"/>
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
-    </row>
-    <row r="46" ht="3" customHeight="1">
-      <c r="A46" s="1" t="n"/>
-      <c r="B46" s="1" t="n"/>
-      <c r="C46" s="1" t="n"/>
-      <c r="D46" s="1" t="n"/>
-      <c r="E46" s="1" t="n"/>
-      <c r="F46" s="1" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n"/>
+      <c r="B52" s="1" t="n"/>
+      <c r="C52" s="1" t="n"/>
+      <c r="D52" s="1" t="n"/>
+      <c r="E52" s="1" t="n"/>
+      <c r="F52" s="1" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="19" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t>Confidential — PECH Group Holdings Ltd — Lagos, Nigeria — pechgroupholdings.tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n"/>
+      <c r="B58" s="1" t="n"/>
+      <c r="C58" s="1" t="n"/>
+      <c r="D58" s="1" t="n"/>
+      <c r="E58" s="1" t="n"/>
+      <c r="F58" s="1" t="n"/>
+      <c r="G58" s="1" t="n"/>
+      <c r="H58" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="16">
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A55:H55"/>
     <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A57:H57"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A54:H54"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;8 PECH Group Holdings Ltd | Confidential</oddHeader>
+    <oddFooter>&amp;C&amp;7 PECH Group Holdings Ltd | Lagos, Nigeria | pechgroupholdings.tech</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/employment_xlsx/PECH_PROFORMA_INVOICE.xlsx
+++ b/employment_xlsx/PECH_PROFORMA_INVOICE.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proforma Invoice" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proforma Form (Fillable)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proforma Invoice'!$A$9:$L$39</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,34 +68,6 @@
       <b val="1"/>
       <color rgb="001B2838"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="000099CC"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <i val="1"/>
-      <color rgb="00F5A623"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="00888888"/>
-      <sz val="7"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00E8F4F8"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="00AAAAAA"/>
-      <sz val="7"/>
     </font>
   </fonts>
   <fills count="9">
@@ -186,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -222,21 +196,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -312,66 +271,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="628650"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="628650"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -663,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -680,31 +579,57 @@
     <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+    <row r="1" ht="6" customHeight="1">
+      <c r="A1" s="1" t="inlineStr"/>
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr"/>
+      <c r="E1" s="1" t="inlineStr"/>
+      <c r="F1" s="1" t="inlineStr"/>
+      <c r="G1" s="1" t="inlineStr"/>
+      <c r="H1" s="1" t="inlineStr"/>
+      <c r="I1" s="1" t="inlineStr"/>
+      <c r="J1" s="1" t="inlineStr"/>
+      <c r="K1" s="1" t="inlineStr"/>
+      <c r="L1" s="1" t="inlineStr"/>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>PECH GROUP HOLDINGS LTD</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Technology &amp; Infrastructure Enablers for People</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="A3" s="1" t="n"/>
-      <c r="B3" s="1" t="n"/>
-      <c r="C3" s="1" t="n"/>
-      <c r="D3" s="1" t="n"/>
-      <c r="E3" s="1" t="n"/>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
-      <c r="H3" s="1" t="n"/>
-    </row>
-    <row r="4" ht="2" customHeight="1">
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>PROFORMA INVOICE</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="4" customHeight="1">
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
@@ -713,151 +638,223 @@
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Confidential</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="8" customHeight="1"/>
-    <row r="7" ht="8" customHeight="1">
-      <c r="A7" s="1" t="inlineStr"/>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr"/>
-      <c r="E7" s="1" t="inlineStr"/>
-      <c r="F7" s="1" t="inlineStr"/>
-      <c r="G7" s="1" t="inlineStr"/>
-      <c r="H7" s="1" t="inlineStr"/>
-      <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr"/>
-      <c r="L7" s="1" t="inlineStr"/>
-    </row>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Pre-Sales Quotation Register  |  CONFIDENTIAL</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="4" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="1" t="n"/>
+      <c r="H6" s="1" t="n"/>
+      <c r="I6" s="1" t="n"/>
+      <c r="J6" s="1" t="n"/>
+      <c r="K6" s="1" t="n"/>
+      <c r="L6" s="1" t="n"/>
+    </row>
+    <row r="7" ht="8" customHeight="1"/>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PROFORMA INVOICE REGISTER</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>PROFORMA INVOICE</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Proforma No.</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Client Name</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Subtotal (NGN)</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>VAT 7.5%</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Valid Until</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>Converted to Invoice</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>Invoice No.</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
+      <c r="A10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="10" t="n"/>
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Pre-Sales Quotation Register  |  CONFIDENTIAL</t>
-        </is>
-      </c>
+      <c r="A11" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="11" t="n"/>
+      <c r="K11" s="11" t="n"/>
+      <c r="L11" s="11" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="1" t="n"/>
-      <c r="H12" s="1" t="n"/>
-      <c r="I12" s="1" t="n"/>
-      <c r="J12" s="1" t="n"/>
-      <c r="K12" s="1" t="n"/>
-      <c r="L12" s="1" t="n"/>
-    </row>
-    <row r="13"/>
+      <c r="A12" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="10" t="n"/>
+      <c r="J12" s="10" t="n"/>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="11" t="n"/>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="11" t="n"/>
+      <c r="L13" s="11" t="n"/>
+    </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PROFORMA INVOICE REGISTER</t>
-        </is>
-      </c>
+      <c r="A14" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="10" t="n"/>
+      <c r="J14" s="10" t="n"/>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Proforma No.</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Client Name</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>Subtotal (NGN)</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>VAT 7.5%</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Valid Until</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>Converted to Invoice</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>Invoice No.</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
+      <c r="A15" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="n"/>
+      <c r="J15" s="11" t="n"/>
+      <c r="K15" s="11" t="n"/>
+      <c r="L15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B16" s="10" t="n"/>
       <c r="C16" s="10" t="n"/>
@@ -873,7 +870,7 @@
     </row>
     <row r="17">
       <c r="A17" s="11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B17" s="11" t="n"/>
       <c r="C17" s="11" t="n"/>
@@ -889,7 +886,7 @@
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="10" t="n"/>
@@ -905,7 +902,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B19" s="11" t="n"/>
       <c r="C19" s="11" t="n"/>
@@ -921,7 +918,7 @@
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="10" t="n"/>
@@ -937,7 +934,7 @@
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B21" s="11" t="n"/>
       <c r="C21" s="11" t="n"/>
@@ -953,7 +950,7 @@
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="n"/>
       <c r="C22" s="10" t="n"/>
@@ -969,7 +966,7 @@
     </row>
     <row r="23">
       <c r="A23" s="11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B23" s="11" t="n"/>
       <c r="C23" s="11" t="n"/>
@@ -985,7 +982,7 @@
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="10" t="n"/>
@@ -1001,7 +998,7 @@
     </row>
     <row r="25">
       <c r="A25" s="11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B25" s="11" t="n"/>
       <c r="C25" s="11" t="n"/>
@@ -1017,7 +1014,7 @@
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="10" t="n"/>
@@ -1033,7 +1030,7 @@
     </row>
     <row r="27">
       <c r="A27" s="11" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B27" s="11" t="n"/>
       <c r="C27" s="11" t="n"/>
@@ -1049,7 +1046,7 @@
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="10" t="n"/>
@@ -1065,7 +1062,7 @@
     </row>
     <row r="29">
       <c r="A29" s="11" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B29" s="11" t="n"/>
       <c r="C29" s="11" t="n"/>
@@ -1081,7 +1078,7 @@
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="10" t="n"/>
@@ -1097,7 +1094,7 @@
     </row>
     <row r="31">
       <c r="A31" s="11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B31" s="11" t="n"/>
       <c r="C31" s="11" t="n"/>
@@ -1113,7 +1110,7 @@
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B32" s="10" t="n"/>
       <c r="C32" s="10" t="n"/>
@@ -1129,7 +1126,7 @@
     </row>
     <row r="33">
       <c r="A33" s="11" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B33" s="11" t="n"/>
       <c r="C33" s="11" t="n"/>
@@ -1145,7 +1142,7 @@
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="10" t="n"/>
@@ -1161,7 +1158,7 @@
     </row>
     <row r="35">
       <c r="A35" s="11" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
@@ -1177,7 +1174,7 @@
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B36" s="10" t="n"/>
       <c r="C36" s="10" t="n"/>
@@ -1193,7 +1190,7 @@
     </row>
     <row r="37">
       <c r="A37" s="11" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B37" s="11" t="n"/>
       <c r="C37" s="11" t="n"/>
@@ -1209,7 +1206,7 @@
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B38" s="10" t="n"/>
       <c r="C38" s="10" t="n"/>
@@ -1225,7 +1222,7 @@
     </row>
     <row r="39">
       <c r="A39" s="11" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
@@ -1239,187 +1236,59 @@
       <c r="K39" s="11" t="n"/>
       <c r="L39" s="11" t="n"/>
     </row>
-    <row r="40">
-      <c r="A40" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
-      <c r="G40" s="10" t="n"/>
-      <c r="H40" s="10" t="n"/>
-      <c r="I40" s="10" t="n"/>
-      <c r="J40" s="10" t="n"/>
-      <c r="K40" s="10" t="n"/>
-      <c r="L40" s="10" t="n"/>
-    </row>
     <row r="41" ht="3" customHeight="1">
-      <c r="A41" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="11" t="n"/>
-      <c r="G41" s="11" t="n"/>
-      <c r="H41" s="11" t="n"/>
-      <c r="I41" s="11" t="n"/>
-      <c r="J41" s="11" t="n"/>
-      <c r="K41" s="11" t="n"/>
-      <c r="L41" s="11" t="n"/>
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="5" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="10" t="n"/>
-      <c r="E42" s="10" t="n"/>
-      <c r="F42" s="10" t="n"/>
-      <c r="G42" s="10" t="n"/>
-      <c r="H42" s="10" t="n"/>
-      <c r="I42" s="10" t="n"/>
-      <c r="J42" s="10" t="n"/>
-      <c r="K42" s="10" t="n"/>
-      <c r="L42" s="10" t="n"/>
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="n"/>
+      <c r="C42" s="13" t="n"/>
+      <c r="D42" s="13" t="n"/>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="13" t="n"/>
+      <c r="G42" s="13" t="n"/>
+      <c r="H42" s="13" t="n"/>
+      <c r="I42" s="13" t="n"/>
+      <c r="J42" s="13" t="n"/>
+      <c r="K42" s="13" t="n"/>
+      <c r="L42" s="13" t="n"/>
     </row>
     <row r="43" ht="3" customHeight="1">
-      <c r="A43" s="11" t="n">
-        <v>28</v>
-      </c>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="11" t="n"/>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="11" t="n"/>
-      <c r="G43" s="11" t="n"/>
-      <c r="H43" s="11" t="n"/>
-      <c r="I43" s="11" t="n"/>
-      <c r="J43" s="11" t="n"/>
-      <c r="K43" s="11" t="n"/>
-      <c r="L43" s="11" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-      <c r="F44" s="10" t="n"/>
-      <c r="G44" s="10" t="n"/>
-      <c r="H44" s="10" t="n"/>
-      <c r="I44" s="10" t="n"/>
-      <c r="J44" s="10" t="n"/>
-      <c r="K44" s="10" t="n"/>
-      <c r="L44" s="10" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="11" t="n"/>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="11" t="n"/>
-      <c r="F45" s="11" t="n"/>
-      <c r="G45" s="11" t="n"/>
-      <c r="H45" s="11" t="n"/>
-      <c r="I45" s="11" t="n"/>
-      <c r="J45" s="11" t="n"/>
-      <c r="K45" s="11" t="n"/>
-      <c r="L45" s="11" t="n"/>
-    </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" s="5" t="n"/>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="5" t="n"/>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="n"/>
-      <c r="L47" s="5" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n"/>
-      <c r="B49" s="1" t="n"/>
-      <c r="C49" s="1" t="n"/>
-      <c r="D49" s="1" t="n"/>
-      <c r="E49" s="1" t="n"/>
-      <c r="F49" s="1" t="n"/>
-      <c r="G49" s="1" t="n"/>
-      <c r="H49" s="1" t="n"/>
-      <c r="I49" s="1" t="n"/>
-      <c r="J49" s="1" t="n"/>
-      <c r="K49" s="1" t="n"/>
-      <c r="L49" s="1" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="19" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="19" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="19" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="20" t="inlineStr">
-        <is>
-          <t>Confidential — PECH Group Holdings Ltd — Lagos, Nigeria — pechgroupholdings.tech</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n"/>
-      <c r="B55" s="1" t="n"/>
-      <c r="C55" s="1" t="n"/>
-      <c r="D55" s="1" t="n"/>
-      <c r="E55" s="1" t="n"/>
-      <c r="F55" s="1" t="n"/>
-      <c r="G55" s="1" t="n"/>
-      <c r="H55" s="1" t="n"/>
+      <c r="A43" s="1" t="n"/>
+      <c r="B43" s="1" t="n"/>
+      <c r="C43" s="1" t="n"/>
+      <c r="D43" s="1" t="n"/>
+      <c r="E43" s="1" t="n"/>
+      <c r="F43" s="1" t="n"/>
+      <c r="G43" s="1" t="n"/>
+      <c r="H43" s="1" t="n"/>
+      <c r="I43" s="1" t="n"/>
+      <c r="J43" s="1" t="n"/>
+      <c r="K43" s="1" t="n"/>
+      <c r="L43" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <autoFilter ref="A9:L39"/>
+  <mergeCells count="5">
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A53:H53"/>
     <mergeCell ref="A42:L42"/>
-    <mergeCell ref="A54:H54"/>
     <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A52:H52"/>
     <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A3:L3"/>
   </mergeCells>
   <dataValidations count="2">
@@ -1431,16 +1300,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;8 PECH Group Holdings Ltd | Confidential</oddHeader>
-    <oddFooter>&amp;C&amp;7 PECH Group Holdings Ltd | Lagos, Nigeria | pechgroupholdings.tech</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1450,7 +1310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1461,105 +1321,127 @@
     <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+    <row r="1" ht="6" customHeight="1">
+      <c r="A1" s="1" t="inlineStr"/>
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr"/>
+      <c r="E1" s="1" t="inlineStr"/>
+      <c r="F1" s="1" t="inlineStr"/>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>PECH GROUP HOLDINGS LTD</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Technology &amp; Infrastructure Enablers for People</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="A3" s="1" t="n"/>
-      <c r="B3" s="1" t="n"/>
-      <c r="C3" s="1" t="n"/>
-      <c r="D3" s="1" t="n"/>
-      <c r="E3" s="1" t="n"/>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
-      <c r="H3" s="1" t="n"/>
-    </row>
-    <row r="4" ht="2" customHeight="1">
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>PROFORMA INVOICE</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="4" customHeight="1">
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Confidential</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="8" customHeight="1"/>
-    <row r="7" ht="8" customHeight="1">
-      <c r="A7" s="1" t="inlineStr"/>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr"/>
-      <c r="E7" s="1" t="inlineStr"/>
-      <c r="F7" s="1" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Pre-Sale Estimate  |  CONFIDENTIAL</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="4" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="1" t="n"/>
+      <c r="E6" s="1" t="n"/>
+      <c r="F6" s="1" t="n"/>
+    </row>
+    <row r="7" ht="8" customHeight="1"/>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PROFORMA DETAILS</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>PROFORMA INVOICE</t>
-        </is>
-      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Proforma No.:</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Date:</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Pre-Sale Estimate  |  CONFIDENTIAL</t>
-        </is>
-      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Valid Until:</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="1" t="n"/>
-      <c r="E12" s="1" t="n"/>
-      <c r="F12" s="1" t="n"/>
-    </row>
-    <row r="13"/>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Project Ref.:</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="n"/>
+    </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PROFORMA DETAILS</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  CLIENT INFORMATION</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Proforma No.:</t>
+          <t>Client Name:</t>
         </is>
       </c>
       <c r="C15" s="15" t="n"/>
@@ -1567,7 +1449,7 @@
     <row r="16" ht="24" customHeight="1">
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>Date:</t>
+          <t>Company:</t>
         </is>
       </c>
       <c r="C16" s="15" t="n"/>
@@ -1575,7 +1457,7 @@
     <row r="17" ht="24" customHeight="1">
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>Valid Until:</t>
+          <t>Address:</t>
         </is>
       </c>
       <c r="C17" s="15" t="n"/>
@@ -1583,31 +1465,35 @@
     <row r="18" ht="24" customHeight="1">
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>Project Ref.:</t>
+          <t>Phone:</t>
         </is>
       </c>
       <c r="C18" s="15" t="n"/>
     </row>
-    <row r="19" ht="24" customHeight="1"/>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CLIENT INFORMATION</t>
-        </is>
-      </c>
+    <row r="19" ht="24" customHeight="1">
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Email:</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="n"/>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>Client Name:</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="n"/>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ITEMS / SERVICES</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Company:</t>
+          <t>Item 1 — Description / Qty / Price:</t>
         </is>
       </c>
       <c r="C22" s="15" t="n"/>
@@ -1615,7 +1501,7 @@
     <row r="23" ht="24" customHeight="1">
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>Address:</t>
+          <t>Item 2 — Description / Qty / Price:</t>
         </is>
       </c>
       <c r="C23" s="15" t="n"/>
@@ -1623,7 +1509,7 @@
     <row r="24" ht="24" customHeight="1">
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>Phone:</t>
+          <t>Item 3 — Description / Qty / Price:</t>
         </is>
       </c>
       <c r="C24" s="15" t="n"/>
@@ -1631,23 +1517,31 @@
     <row r="25" ht="24" customHeight="1">
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Email:</t>
+          <t>Item 4 — Description / Qty / Price:</t>
         </is>
       </c>
       <c r="C25" s="15" t="n"/>
     </row>
-    <row r="26" ht="24" customHeight="1"/>
+    <row r="26" ht="24" customHeight="1">
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Item 5 — Description / Qty / Price:</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="n"/>
+    </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ITEMS / SERVICES</t>
-        </is>
-      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Item 6 — Description / Qty / Price:</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="n"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>Item 1 — Description / Qty / Price:</t>
+          <t>Item 7 — Description / Qty / Price:</t>
         </is>
       </c>
       <c r="C28" s="15" t="n"/>
@@ -1655,31 +1549,27 @@
     <row r="29" ht="24" customHeight="1">
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Item 2 — Description / Qty / Price:</t>
+          <t>Item 8 — Description / Qty / Price:</t>
         </is>
       </c>
       <c r="C29" s="15" t="n"/>
     </row>
-    <row r="30">
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>Item 3 — Description / Qty / Price:</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="n"/>
-    </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>Item 4 — Description / Qty / Price:</t>
-        </is>
-      </c>
-      <c r="C31" s="15" t="n"/>
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="8" t="n"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>Item 5 — Description / Qty / Price:</t>
+          <t>Subtotal:</t>
         </is>
       </c>
       <c r="C32" s="15" t="n"/>
@@ -1687,7 +1577,7 @@
     <row r="33" ht="24" customHeight="1">
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>Item 6 — Description / Qty / Price:</t>
+          <t>VAT @ 7.5%:</t>
         </is>
       </c>
       <c r="C33" s="15" t="n"/>
@@ -1695,7 +1585,7 @@
     <row r="34" ht="24" customHeight="1">
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>Item 7 — Description / Qty / Price:</t>
+          <t>Discount:</t>
         </is>
       </c>
       <c r="C34" s="15" t="n"/>
@@ -1703,31 +1593,35 @@
     <row r="35" ht="24" customHeight="1">
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Item 8 — Description / Qty / Price:</t>
+          <t>GRAND TOTAL:</t>
         </is>
       </c>
       <c r="C35" s="15" t="n"/>
     </row>
-    <row r="36" ht="24" customHeight="1"/>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  SUMMARY</t>
-        </is>
-      </c>
+    <row r="36" ht="24" customHeight="1">
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Amount in Words:</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="n"/>
     </row>
     <row r="38" ht="26" customHeight="1">
-      <c r="B38" s="14" t="inlineStr">
-        <is>
-          <t>Subtotal:</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="n"/>
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AUTHORIZATION</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>VAT @ 7.5%:</t>
+          <t>Prepared By:</t>
         </is>
       </c>
       <c r="C39" s="15" t="n"/>
@@ -1735,7 +1629,7 @@
     <row r="40" ht="24" customHeight="1">
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>Discount:</t>
+          <t>Signature:</t>
         </is>
       </c>
       <c r="C40" s="15" t="n"/>
@@ -1743,143 +1637,52 @@
     <row r="41" ht="24" customHeight="1">
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>GRAND TOTAL:</t>
+          <t>Date:</t>
         </is>
       </c>
       <c r="C41" s="15" t="n"/>
     </row>
-    <row r="42">
-      <c r="B42" s="14" t="inlineStr">
-        <is>
-          <t>Amount in Words:</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="n"/>
-    </row>
-    <row r="43"/>
     <row r="44" ht="3" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  AUTHORIZATION</t>
-        </is>
-      </c>
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="14" t="inlineStr">
-        <is>
-          <t>Prepared By:</t>
-        </is>
-      </c>
-      <c r="C45" s="15" t="n"/>
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="n"/>
+      <c r="C45" s="13" t="n"/>
+      <c r="D45" s="13" t="n"/>
+      <c r="E45" s="13" t="n"/>
+      <c r="F45" s="13" t="n"/>
     </row>
     <row r="46" ht="3" customHeight="1">
-      <c r="B46" s="14" t="inlineStr">
-        <is>
-          <t>Signature:</t>
-        </is>
-      </c>
-      <c r="C46" s="15" t="n"/>
-    </row>
-    <row r="47">
-      <c r="B47" s="14" t="inlineStr">
-        <is>
-          <t>Date:</t>
-        </is>
-      </c>
-      <c r="C47" s="15" t="n"/>
-    </row>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50">
-      <c r="A50" s="5" t="n"/>
-      <c r="B50" s="5" t="n"/>
-      <c r="C50" s="5" t="n"/>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="12" t="inlineStr">
-        <is>
-          <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n"/>
-      <c r="B52" s="1" t="n"/>
-      <c r="C52" s="1" t="n"/>
-      <c r="D52" s="1" t="n"/>
-      <c r="E52" s="1" t="n"/>
-      <c r="F52" s="1" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="19" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="19" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="19" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="20" t="inlineStr">
-        <is>
-          <t>Confidential — PECH Group Holdings Ltd — Lagos, Nigeria — pechgroupholdings.tech</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="n"/>
-      <c r="B58" s="1" t="n"/>
-      <c r="C58" s="1" t="n"/>
-      <c r="D58" s="1" t="n"/>
-      <c r="E58" s="1" t="n"/>
-      <c r="F58" s="1" t="n"/>
-      <c r="G58" s="1" t="n"/>
-      <c r="H58" s="1" t="n"/>
+      <c r="A46" s="1" t="n"/>
+      <c r="B46" s="1" t="n"/>
+      <c r="C46" s="1" t="n"/>
+      <c r="D46" s="1" t="n"/>
+      <c r="E46" s="1" t="n"/>
+      <c r="F46" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="9">
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A56:H56"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A55:H55"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A57:H57"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A54:H54"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;8 PECH Group Holdings Ltd | Confidential</oddHeader>
-    <oddFooter>&amp;C&amp;7 PECH Group Holdings Ltd | Lagos, Nigeria | pechgroupholdings.tech</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/employment_xlsx/PECH_PROFORMA_INVOICE.xlsx
+++ b/employment_xlsx/PECH_PROFORMA_INVOICE.xlsx
@@ -97,14 +97,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000099CC"/>
-        <bgColor rgb="000099CC"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="000099CC"/>
+        <bgColor rgb="000099CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -120,13 +120,19 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
     </border>
     <border>
       <left style="thin">
@@ -162,39 +168,39 @@
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -675,566 +681,579 @@
       <c r="K6" s="1" t="n"/>
       <c r="L6" s="1" t="n"/>
     </row>
-    <row r="7" ht="8" customHeight="1"/>
+    <row r="7" ht="8" customHeight="1">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="7" t="n"/>
+      <c r="L7" s="7" t="n"/>
+    </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  PROFORMA INVOICE REGISTER</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
-      <c r="K8" s="8" t="n"/>
-      <c r="L8" s="8" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
+      <c r="L8" s="9" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Proforma No.</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Client Name</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Subtotal (NGN)</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>VAT 7.5%</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>Valid Until</t>
         </is>
       </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>Converted to Invoice</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="10" t="inlineStr">
         <is>
           <t>Invoice No.</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="L9" s="10" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="10" t="n">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="10" t="n"/>
-      <c r="I10" s="10" t="n"/>
-      <c r="J10" s="10" t="n"/>
-      <c r="K10" s="10" t="n"/>
-      <c r="L10" s="10" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="11" t="n"/>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="11" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="11" t="n"/>
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="11" t="n"/>
+      <c r="K10" s="11" t="n"/>
+      <c r="L10" s="11" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="11" t="n"/>
-      <c r="J11" s="11" t="n"/>
-      <c r="K11" s="11" t="n"/>
-      <c r="L11" s="11" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="n">
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="12" t="n"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="12" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="n"/>
-      <c r="K12" s="10" t="n"/>
-      <c r="L12" s="10" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="11" t="n"/>
+      <c r="J12" s="11" t="n"/>
+      <c r="K12" s="11" t="n"/>
+      <c r="L12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="11" t="n"/>
-      <c r="K13" s="11" t="n"/>
-      <c r="L13" s="11" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="n">
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="12" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="10" t="n"/>
-      <c r="I14" s="10" t="n"/>
-      <c r="J14" s="10" t="n"/>
-      <c r="K14" s="10" t="n"/>
-      <c r="L14" s="10" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="11" t="n"/>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="11" t="n"/>
+      <c r="K14" s="11" t="n"/>
+      <c r="L14" s="11" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="11" t="n"/>
-      <c r="L15" s="11" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="n">
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="12" t="n"/>
+      <c r="I15" s="12" t="n"/>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="12" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="10" t="n"/>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-      <c r="H16" s="10" t="n"/>
-      <c r="I16" s="10" t="n"/>
-      <c r="J16" s="10" t="n"/>
-      <c r="K16" s="10" t="n"/>
-      <c r="L16" s="10" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="n">
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="11" t="n"/>
+      <c r="I16" s="11" t="n"/>
+      <c r="J16" s="11" t="n"/>
+      <c r="K16" s="11" t="n"/>
+      <c r="L16" s="11" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n"/>
-      <c r="I17" s="11" t="n"/>
-      <c r="J17" s="11" t="n"/>
-      <c r="K17" s="11" t="n"/>
-      <c r="L17" s="11" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="n">
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
-      <c r="H18" s="10" t="n"/>
-      <c r="I18" s="10" t="n"/>
-      <c r="J18" s="10" t="n"/>
-      <c r="K18" s="10" t="n"/>
-      <c r="L18" s="10" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="n">
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="11" t="n"/>
+      <c r="I18" s="11" t="n"/>
+      <c r="J18" s="11" t="n"/>
+      <c r="K18" s="11" t="n"/>
+      <c r="L18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="n"/>
-      <c r="I19" s="11" t="n"/>
-      <c r="J19" s="11" t="n"/>
-      <c r="K19" s="11" t="n"/>
-      <c r="L19" s="11" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="n">
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-      <c r="H20" s="10" t="n"/>
-      <c r="I20" s="10" t="n"/>
-      <c r="J20" s="10" t="n"/>
-      <c r="K20" s="10" t="n"/>
-      <c r="L20" s="10" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="n">
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="11" t="n"/>
+      <c r="I20" s="11" t="n"/>
+      <c r="J20" s="11" t="n"/>
+      <c r="K20" s="11" t="n"/>
+      <c r="L20" s="11" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
-      <c r="J21" s="11" t="n"/>
-      <c r="K21" s="11" t="n"/>
-      <c r="L21" s="11" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="12" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="10" t="n"/>
-      <c r="I22" s="10" t="n"/>
-      <c r="J22" s="10" t="n"/>
-      <c r="K22" s="10" t="n"/>
-      <c r="L22" s="10" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="n">
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="11" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="11" t="n"/>
+      <c r="I22" s="11" t="n"/>
+      <c r="J22" s="11" t="n"/>
+      <c r="K22" s="11" t="n"/>
+      <c r="L22" s="11" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="n"/>
-      <c r="I23" s="11" t="n"/>
-      <c r="J23" s="11" t="n"/>
-      <c r="K23" s="11" t="n"/>
-      <c r="L23" s="11" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n">
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="10" t="n"/>
-      <c r="H24" s="10" t="n"/>
-      <c r="I24" s="10" t="n"/>
-      <c r="J24" s="10" t="n"/>
-      <c r="K24" s="10" t="n"/>
-      <c r="L24" s="10" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="n">
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="11" t="n"/>
+      <c r="I24" s="11" t="n"/>
+      <c r="J24" s="11" t="n"/>
+      <c r="K24" s="11" t="n"/>
+      <c r="L24" s="11" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="11" t="n"/>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="11" t="n"/>
-      <c r="I25" s="11" t="n"/>
-      <c r="J25" s="11" t="n"/>
-      <c r="K25" s="11" t="n"/>
-      <c r="L25" s="11" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="n">
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="10" t="n"/>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="10" t="n"/>
-      <c r="H26" s="10" t="n"/>
-      <c r="I26" s="10" t="n"/>
-      <c r="J26" s="10" t="n"/>
-      <c r="K26" s="10" t="n"/>
-      <c r="L26" s="10" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="n">
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="11" t="n"/>
+      <c r="G26" s="11" t="n"/>
+      <c r="H26" s="11" t="n"/>
+      <c r="I26" s="11" t="n"/>
+      <c r="J26" s="11" t="n"/>
+      <c r="K26" s="11" t="n"/>
+      <c r="L26" s="11" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="n"/>
-      <c r="G27" s="11" t="n"/>
-      <c r="H27" s="11" t="n"/>
-      <c r="I27" s="11" t="n"/>
-      <c r="J27" s="11" t="n"/>
-      <c r="K27" s="11" t="n"/>
-      <c r="L27" s="11" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="n">
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
-      <c r="H28" s="10" t="n"/>
-      <c r="I28" s="10" t="n"/>
-      <c r="J28" s="10" t="n"/>
-      <c r="K28" s="10" t="n"/>
-      <c r="L28" s="10" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="n">
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="11" t="n"/>
+      <c r="I28" s="11" t="n"/>
+      <c r="J28" s="11" t="n"/>
+      <c r="K28" s="11" t="n"/>
+      <c r="L28" s="11" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="11" t="n"/>
-      <c r="I29" s="11" t="n"/>
-      <c r="J29" s="11" t="n"/>
-      <c r="K29" s="11" t="n"/>
-      <c r="L29" s="11" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="n">
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="10" t="n"/>
-      <c r="H30" s="10" t="n"/>
-      <c r="I30" s="10" t="n"/>
-      <c r="J30" s="10" t="n"/>
-      <c r="K30" s="10" t="n"/>
-      <c r="L30" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="n">
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="11" t="n"/>
+      <c r="I30" s="11" t="n"/>
+      <c r="J30" s="11" t="n"/>
+      <c r="K30" s="11" t="n"/>
+      <c r="L30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="11" t="n"/>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="11" t="n"/>
-      <c r="I31" s="11" t="n"/>
-      <c r="J31" s="11" t="n"/>
-      <c r="K31" s="11" t="n"/>
-      <c r="L31" s="11" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="n">
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="10" t="n"/>
-      <c r="H32" s="10" t="n"/>
-      <c r="I32" s="10" t="n"/>
-      <c r="J32" s="10" t="n"/>
-      <c r="K32" s="10" t="n"/>
-      <c r="L32" s="10" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="n">
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="11" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="11" t="n"/>
+      <c r="I32" s="11" t="n"/>
+      <c r="J32" s="11" t="n"/>
+      <c r="K32" s="11" t="n"/>
+      <c r="L32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="11" t="n"/>
-      <c r="I33" s="11" t="n"/>
-      <c r="J33" s="11" t="n"/>
-      <c r="K33" s="11" t="n"/>
-      <c r="L33" s="11" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="n">
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12" t="n"/>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="12" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="10" t="n"/>
-      <c r="H34" s="10" t="n"/>
-      <c r="I34" s="10" t="n"/>
-      <c r="J34" s="10" t="n"/>
-      <c r="K34" s="10" t="n"/>
-      <c r="L34" s="10" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="n">
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="11" t="n"/>
+      <c r="G34" s="11" t="n"/>
+      <c r="H34" s="11" t="n"/>
+      <c r="I34" s="11" t="n"/>
+      <c r="J34" s="11" t="n"/>
+      <c r="K34" s="11" t="n"/>
+      <c r="L34" s="11" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="11" t="n"/>
-      <c r="F35" s="11" t="n"/>
-      <c r="G35" s="11" t="n"/>
-      <c r="H35" s="11" t="n"/>
-      <c r="I35" s="11" t="n"/>
-      <c r="J35" s="11" t="n"/>
-      <c r="K35" s="11" t="n"/>
-      <c r="L35" s="11" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="n">
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="12" t="n"/>
+      <c r="H35" s="12" t="n"/>
+      <c r="I35" s="12" t="n"/>
+      <c r="J35" s="12" t="n"/>
+      <c r="K35" s="12" t="n"/>
+      <c r="L35" s="12" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="10" t="n"/>
-      <c r="H36" s="10" t="n"/>
-      <c r="I36" s="10" t="n"/>
-      <c r="J36" s="10" t="n"/>
-      <c r="K36" s="10" t="n"/>
-      <c r="L36" s="10" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="n">
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="11" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="11" t="n"/>
+      <c r="I36" s="11" t="n"/>
+      <c r="J36" s="11" t="n"/>
+      <c r="K36" s="11" t="n"/>
+      <c r="L36" s="11" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="11" t="n"/>
-      <c r="I37" s="11" t="n"/>
-      <c r="J37" s="11" t="n"/>
-      <c r="K37" s="11" t="n"/>
-      <c r="L37" s="11" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="n">
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="12" t="n"/>
+      <c r="G37" s="12" t="n"/>
+      <c r="H37" s="12" t="n"/>
+      <c r="I37" s="12" t="n"/>
+      <c r="J37" s="12" t="n"/>
+      <c r="K37" s="12" t="n"/>
+      <c r="L37" s="12" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="10" t="n"/>
-      <c r="E38" s="10" t="n"/>
-      <c r="F38" s="10" t="n"/>
-      <c r="G38" s="10" t="n"/>
-      <c r="H38" s="10" t="n"/>
-      <c r="I38" s="10" t="n"/>
-      <c r="J38" s="10" t="n"/>
-      <c r="K38" s="10" t="n"/>
-      <c r="L38" s="10" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="n">
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="n"/>
+      <c r="G38" s="11" t="n"/>
+      <c r="H38" s="11" t="n"/>
+      <c r="I38" s="11" t="n"/>
+      <c r="J38" s="11" t="n"/>
+      <c r="K38" s="11" t="n"/>
+      <c r="L38" s="11" t="n"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="11" t="n"/>
-      <c r="G39" s="11" t="n"/>
-      <c r="H39" s="11" t="n"/>
-      <c r="I39" s="11" t="n"/>
-      <c r="J39" s="11" t="n"/>
-      <c r="K39" s="11" t="n"/>
-      <c r="L39" s="11" t="n"/>
+      <c r="B39" s="12" t="n"/>
+      <c r="C39" s="12" t="n"/>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="12" t="n"/>
+      <c r="G39" s="12" t="n"/>
+      <c r="H39" s="12" t="n"/>
+      <c r="I39" s="12" t="n"/>
+      <c r="J39" s="12" t="n"/>
+      <c r="K39" s="12" t="n"/>
+      <c r="L39" s="12" t="n"/>
     </row>
     <row r="41" ht="3" customHeight="1">
       <c r="A41" s="5" t="n"/>
@@ -1250,23 +1269,23 @@
       <c r="K41" s="5" t="n"/>
       <c r="L41" s="5" t="n"/>
     </row>
-    <row r="42">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="n"/>
-      <c r="C42" s="13" t="n"/>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="13" t="n"/>
-      <c r="H42" s="13" t="n"/>
-      <c r="I42" s="13" t="n"/>
-      <c r="J42" s="13" t="n"/>
-      <c r="K42" s="13" t="n"/>
-      <c r="L42" s="13" t="n"/>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="7" t="n"/>
+      <c r="F42" s="7" t="n"/>
+      <c r="G42" s="7" t="n"/>
+      <c r="H42" s="7" t="n"/>
+      <c r="I42" s="7" t="n"/>
+      <c r="J42" s="7" t="n"/>
+      <c r="K42" s="7" t="n"/>
+      <c r="L42" s="7" t="n"/>
     </row>
     <row r="43" ht="3" customHeight="1">
       <c r="A43" s="1" t="n"/>
@@ -1381,18 +1400,25 @@
       <c r="E6" s="1" t="n"/>
       <c r="F6" s="1" t="n"/>
     </row>
-    <row r="7" ht="8" customHeight="1"/>
+    <row r="7" ht="8" customHeight="1">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+    </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  PROFORMA DETAILS</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="B9" s="14" t="inlineStr">
@@ -1427,16 +1453,16 @@
       <c r="C12" s="15" t="n"/>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  CLIENT INFORMATION</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="B15" s="14" t="inlineStr">
@@ -1479,16 +1505,16 @@
       <c r="C19" s="15" t="n"/>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  ITEMS / SERVICES</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="B22" s="14" t="inlineStr">
@@ -1555,16 +1581,16 @@
       <c r="C29" s="15" t="n"/>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  SUMMARY</t>
         </is>
       </c>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="8" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="B32" s="14" t="inlineStr">
@@ -1607,16 +1633,16 @@
       <c r="C36" s="15" t="n"/>
     </row>
     <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  AUTHORIZATION</t>
         </is>
       </c>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="B39" s="14" t="inlineStr">
@@ -1650,17 +1676,17 @@
       <c r="E44" s="5" t="n"/>
       <c r="F44" s="5" t="n"/>
     </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
-        </is>
-      </c>
-      <c r="B45" s="13" t="n"/>
-      <c r="C45" s="13" t="n"/>
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="7" t="n"/>
+      <c r="E45" s="7" t="n"/>
+      <c r="F45" s="7" t="n"/>
     </row>
     <row r="46" ht="3" customHeight="1">
       <c r="A46" s="1" t="n"/>
